--- a/static/data/exports/Retro_AS_GE_2009.xlsx
+++ b/static/data/exports/Retro_AS_GE_2009.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/data/exports/Retro_AS_GE_2009.xlsx
+++ b/static/data/exports/Retro_AS_GE_2009.xlsx
@@ -1337,11 +1337,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1725397</v>
+        <v>1725396</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Malati Roy</t>
+          <t>Debasish Das</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Malati Roy</t>
+          <t>Debasish Das</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1399,11 +1399,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1725396</v>
+        <v>1725397</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Debasish Das</t>
+          <t>Malati Roy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Debasish Das</t>
+          <t>Malati Roy</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -7599,11 +7599,11 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1725497</v>
+        <v>1725498</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Joy Das</t>
+          <t>Ranjan Namasudra</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Joy Das</t>
+          <t>Ranjan Namasudra</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7661,11 +7661,11 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1725498</v>
+        <v>1725497</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ranjan Namasudra</t>
+          <t>Joy Das</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Ranjan Namasudra</t>
+          <t>Joy Das</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8166,11 +8166,11 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E125" t="n">
         <v>2625</v>
@@ -9158,11 +9158,11 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E141" t="n">
         <v>855</v>
@@ -10150,11 +10150,11 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E157" t="n">
         <v>2489</v>
@@ -11142,11 +11142,11 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E173" t="n">
         <v>1480</v>
@@ -12258,11 +12258,11 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E191" t="n">
         <v>942</v>
@@ -13126,11 +13126,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E205" t="n">
         <v>1980</v>
@@ -14118,11 +14118,11 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E221" t="n">
         <v>1459</v>
@@ -22054,11 +22054,11 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E349" t="n">
         <v>4583</v>
@@ -23108,11 +23108,11 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E366" t="n">
         <v>4430</v>
@@ -23976,11 +23976,11 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E380" t="n">
         <v>1275</v>
@@ -27758,11 +27758,11 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E441" t="n">
         <v>5387</v>
@@ -28688,11 +28688,11 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E456" t="n">
         <v>2003</v>
@@ -29556,11 +29556,11 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E470" t="n">
         <v>4631</v>
@@ -30424,11 +30424,11 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D484" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E484" t="n">
         <v>1493</v>
@@ -31292,11 +31292,11 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E498" t="n">
         <v>7622</v>
@@ -32160,11 +32160,11 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E512" t="n">
         <v>2495</v>
@@ -42328,11 +42328,11 @@
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D676" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E676" t="n">
         <v>2058</v>
@@ -49272,11 +49272,11 @@
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D788" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E788" t="n">
         <v>3652</v>
@@ -50140,11 +50140,11 @@
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D802" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E802" t="n">
         <v>2741</v>
@@ -51070,11 +51070,11 @@
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D817" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E817" t="n">
         <v>2178</v>
@@ -51938,11 +51938,11 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D831" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E831" t="n">
         <v>11621</v>
@@ -52868,11 +52868,11 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D846" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E846" t="n">
         <v>6718</v>
@@ -53798,11 +53798,11 @@
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D861" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E861" t="n">
         <v>4221</v>
@@ -54790,11 +54790,11 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D877" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E877" t="n">
         <v>2849</v>
@@ -55277,20 +55277,20 @@
     </row>
     <row r="885">
       <c r="A885" t="n">
-        <v>1726266</v>
+        <v>1726267</v>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>Reginold V. Johnson</t>
+          <t>Kalyan Kumar Deori Bharali</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>RSPS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D885" t="n">
-        <v>19939</v>
+        <v>19861</v>
       </c>
       <c r="E885" t="n">
         <v>560</v>
@@ -55314,12 +55314,12 @@
       </c>
       <c r="K885" t="inlineStr">
         <is>
-          <t>Reginold V. Johnson</t>
+          <t>Kalyan Kumar Deori Bharali</t>
         </is>
       </c>
       <c r="L885" t="inlineStr">
         <is>
-          <t>RSPS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q885" t="b">
@@ -55339,20 +55339,20 @@
     </row>
     <row r="886">
       <c r="A886" t="n">
-        <v>1726267</v>
+        <v>1726266</v>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>Kalyan Kumar Deori Bharali</t>
+          <t>Reginold V. Johnson</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>RSPS</t>
         </is>
       </c>
       <c r="D886" t="n">
-        <v>19861</v>
+        <v>19939</v>
       </c>
       <c r="E886" t="n">
         <v>560</v>
@@ -55376,12 +55376,12 @@
       </c>
       <c r="K886" t="inlineStr">
         <is>
-          <t>Kalyan Kumar Deori Bharali</t>
+          <t>Reginold V. Johnson</t>
         </is>
       </c>
       <c r="L886" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>RSPS</t>
         </is>
       </c>
       <c r="Q886" t="b">
@@ -55720,11 +55720,11 @@
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D892" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E892" t="n">
         <v>1663</v>
@@ -74692,11 +74692,11 @@
       </c>
       <c r="C1198" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1198" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E1198" t="n">
         <v>1063</v>
